--- a/AAII_Financials/Yearly/NXT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NXT_YR_FIN.xlsx
@@ -1861,10 +1861,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>50200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>135100</v>
+        <v>186400</v>
       </c>
       <c r="E45" s="3">
-        <v>38300</v>
+        <v>88500</v>
       </c>
       <c r="F45" s="3">
         <v>187200</v>
